--- a/runs/RELX/2026-10-14/bear/scratch/b_beta_damo5y/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_beta_damo5y/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1965.577119620572</v>
+        <v>2033.655642735944</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.11425</v>
+        <v>0.10469</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.10569116504</v>
+        <v>0.09735656584000001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10900.21575546084</v>
+        <v>11100.72073223604</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>33600.56457314103</v>
+        <v>37220.77748680738</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>21379.34016556922</v>
+        <v>24503.0694716156</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>32279.55592103006</v>
+        <v>35603.79020385163</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>25282.55592103006</v>
+        <v>28606.79020385163</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>24245.92976117225</v>
+        <v>27654.71168402164</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>13.90443815621109</v>
+        <v>15.85928987363923</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1390.443815621109</v>
+        <v>1585.928987363923</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4982158731</v>
+        <v>-0.4276690771</v>
       </c>
     </row>
   </sheetData>
